--- a/LISTAS_ORDENADAS/MA/Soportes y escuadras/SOPORTE U LIDIMA.xlsx
+++ b/LISTAS_ORDENADAS/MA/Soportes y escuadras/SOPORTE U LIDIMA.xlsx
@@ -794,14 +794,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="19" t="n">
-        <v>45189.54995376568</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -847,20 +843,6 @@
       </c>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26" ht="18" customHeight="1" s="1">
       <c r="A26" s="21" t="inlineStr">
         <is>
@@ -947,7 +929,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
@@ -957,15 +938,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
